--- a/shop_data.xlsx
+++ b/shop_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -44,7 +44,7 @@
     <t>admin</t>
   </si>
   <si>
-    <t>fpBkz1vhRy/DvoF6U+3pAQ==$+atC+86bHq/l3DEqlz+rAa7NpA6U6HggicgfkHnpgz0=</t>
+    <t>HtYtJE6FOJiSLy2cfnUFNw==$he1id5iEUv3GXBJLmaTu3idKZhsWLzS4f5fQGGqWEA8=</t>
   </si>
   <si>
     <t>13800138000</t>
@@ -53,7 +53,7 @@
     <t>admin@qq.com</t>
   </si>
   <si>
-    <t>2026-09-19 09:37:39</t>
+    <t>2026-09-29 23:51:53</t>
   </si>
   <si>
     <t>等级</t>
@@ -68,7 +68,7 @@
     <t>user123</t>
   </si>
   <si>
-    <t>Bo1HDk4p2F4PyNLiSdzZ5w==$eNiJwtIM8Q4ZsUXxp9IH9gOby1GPZTNGxOouiBl1BeM=</t>
+    <t>eKnnVWYQRcEt55tiSVrFRA==$p6kHcTQ6CcN4HrYaOuPrhWjiq9j6KKQawfJRT4jOXGM=</t>
   </si>
   <si>
     <t>13900139000</t>
@@ -80,19 +80,43 @@
     <t/>
   </si>
   <si>
-    <t>扬的iphone</t>
-  </si>
-  <si>
-    <t>DWfuWFFUj5jcOgbQQC82+A==$7u0pkNOB5QsAmgtXYPZgc+b0MFMcLq95+PuZAEsOXgw=</t>
-  </si>
-  <si>
-    <t>12233335555</t>
-  </si>
-  <si>
-    <t>2381945409@qq.com</t>
-  </si>
-  <si>
-    <t>2026-09-19 09:42:38</t>
+    <t>yyyyyyyyy</t>
+  </si>
+  <si>
+    <t>/4+3EwD0GQbSnjkdiEXNQQ==$kLsDQFNHH3jkDDvPAE/2lD/mp9sK4sSxDzhQr5maLcg=</t>
+  </si>
+  <si>
+    <t>13344445555</t>
+  </si>
+  <si>
+    <t>990401626@qq.com</t>
+  </si>
+  <si>
+    <t>2026-09-29 23:52:42</t>
+  </si>
+  <si>
+    <t>wwwwww</t>
+  </si>
+  <si>
+    <t>hi/9Hm0ndxj3ejeVfC+T6g==$Y/EWfJed8riXxLYX4IjdU/l4aaXUsp/hF9UO6RmaP5o=</t>
+  </si>
+  <si>
+    <t>12233334444</t>
+  </si>
+  <si>
+    <t>2026-09-30 16:49:11</t>
+  </si>
+  <si>
+    <t>wwwwwwww</t>
+  </si>
+  <si>
+    <t>5ehE01VVWWGXOSybMOPbaQ==$H9bGwdAU31IlcMPH32pGg05ioXRBRrhNNSFavRky2CA=</t>
+  </si>
+  <si>
+    <t>13266668888</t>
+  </si>
+  <si>
+    <t>2026-10-02 21:01:31</t>
   </si>
   <si>
     <t>商品ID</t>
@@ -159,18 +183,6 @@
   </si>
   <si>
     <t>商品明细</t>
-  </si>
-  <si>
-    <t>ORD1789782248320</t>
-  </si>
-  <si>
-    <t>2026-09-19 09:44:08</t>
-  </si>
-  <si>
-    <t>支付宝</t>
-  </si>
-  <si>
-    <t>101:3</t>
   </si>
 </sst>
 </file>
@@ -277,7 +289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -376,12 +388,82 @@
         <v>0.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>20997.0</v>
+        <v>0.0</v>
       </c>
       <c r="K3" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>1003.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>1004.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K5" t="s" s="0">
         <v>20</v>
       </c>
     </row>
@@ -397,28 +479,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -426,16 +508,16 @@
         <v>101.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n" s="0">
         <v>5000.0</v>
@@ -444,7 +526,7 @@
         <v>6999.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="3">
@@ -452,16 +534,16 @@
         <v>102.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>3000.0</v>
@@ -480,47 +562,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="B2" t="n" s="0">
-        <v>1002.0</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>20997.0</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
